--- a/data/Key Metrics at a Glance.xlsx
+++ b/data/Key Metrics at a Glance.xlsx
@@ -589,6 +589,15 @@
           <t>Total Revenue</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>25463435</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25375643</v>
+      </c>
+      <c r="E10" t="n">
+        <v>87792</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -601,6 +610,15 @@
           <t>Total Costs</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>24853371</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24699964</v>
+      </c>
+      <c r="E11" t="n">
+        <v>153407</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -612,6 +630,15 @@
         <is>
           <t>Operating Margin</t>
         </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/Key Metrics at a Glance.xlsx
+++ b/data/Key Metrics at a Glance.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,6 +477,17 @@
           <t>Annual cwt</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>361247</v>
+      </c>
+      <c r="D2" t="n">
+        <v>345778</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
       <c r="F2">
         <f>C2*11.63</f>
         <v/>
@@ -497,6 +508,17 @@
           <t>Lbs/Cow/Day</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -509,6 +531,17 @@
           <t>Butterfat %</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -521,6 +554,17 @@
           <t>SCC (cells/mL)</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+25%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -544,6 +588,9 @@
         <is>
           <t>Labor Hrs/cwt</t>
         </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.191</v>
       </c>
       <c r="F7">
         <f>C7/11.63</f>

--- a/data/Key Metrics at a Glance.xlsx
+++ b/data/Key Metrics at a Glance.xlsx
@@ -1,37 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviaarkema/Documents/Strategic Planning/CD_StrategicPlanning/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56039BB3-74DD-F845-86AA-13C12446082A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>TTM Jul 2026</t>
+  </si>
+  <si>
+    <t>TTM Jul 2025</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>TTM Jul 2026 (gal)</t>
+  </si>
+  <si>
+    <t>TTM Jul 2025 (gal)</t>
+  </si>
+  <si>
+    <t>Milk Production</t>
+  </si>
+  <si>
+    <t>Annual cwt</t>
+  </si>
+  <si>
+    <t>+4.5%</t>
+  </si>
+  <si>
+    <t>Lbs/Cow/Day</t>
+  </si>
+  <si>
+    <t>+3.2%</t>
+  </si>
+  <si>
+    <t>Milk Quality</t>
+  </si>
+  <si>
+    <t>Butterfat %</t>
+  </si>
+  <si>
+    <t>flat</t>
+  </si>
+  <si>
+    <t>SCC (cells/mL)</t>
+  </si>
+  <si>
+    <t>+25%</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>Utilization Rate</t>
+  </si>
+  <si>
+    <t>Labor Hrs/cwt</t>
+  </si>
+  <si>
+    <t>Crops</t>
+  </si>
+  <si>
+    <t>Corn Silage (t/a)</t>
+  </si>
+  <si>
+    <t>Alfalfa (t/a)</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Total Revenue (Ordinary Income)</t>
+  </si>
+  <si>
+    <t>Total Costs (COGS + OPEx)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +156,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,279 +459,209 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>TTM Jul 2026</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>TTM Jul 2025</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>TTM Jul 2026 (gal)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>TTM Jul 2025 (gal)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Milk Production</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Annual cwt</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
         <v>361247</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>345778</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>+4.5%</t>
-        </is>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
       <c r="F2">
         <f>C2*11.63</f>
-        <v/>
+        <v>4201302.6100000003</v>
       </c>
       <c r="G2">
         <f>D2*11.63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Milk Production</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Lbs/Cow/Day</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+        <v>4021398.14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
         <v>96</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>93</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>+3.2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Milk Quality</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Butterfat %</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>flat</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Milk Quality</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SCC (cells/mL)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D4">
+        <v>3.9E-2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
         <v>250000</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>200000</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>+25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Utilization Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Labor Hrs/cwt</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
         <v>0.191</v>
       </c>
       <c r="F7">
         <f>C7/11.63</f>
-        <v/>
+        <v>1.642304385210662E-2</v>
       </c>
       <c r="G7">
         <f>D7/11.63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Crops</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Corn Silage (t/a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Crops</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Alfalfa (t/a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>25463435</v>
-      </c>
-      <c r="D10" t="n">
-        <v>25375643</v>
-      </c>
-      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>25483840</v>
+      </c>
+      <c r="D10">
+        <v>26079541</v>
+      </c>
+      <c r="E10">
         <v>87792</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Total Costs</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>24853371</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24699964</v>
-      </c>
-      <c r="E11" t="n">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <f>4341828+20387243</f>
+        <v>24729071</v>
+      </c>
+      <c r="D11">
+        <f>7826513+17830008</f>
+        <v>25656521</v>
+      </c>
+      <c r="E11">
         <v>153407</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Operating Margin</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
         <v>2.4</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>2.7</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>-0.3</v>
       </c>
     </row>

--- a/data/Key Metrics at a Glance.xlsx
+++ b/data/Key Metrics at a Glance.xlsx
@@ -1,143 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviaarkema/Documents/Strategic Planning/CD_StrategicPlanning/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56039BB3-74DD-F845-86AA-13C12446082A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
-  <si>
-    <t>Area</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>TTM Jul 2026</t>
-  </si>
-  <si>
-    <t>TTM Jul 2025</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>TTM Jul 2026 (gal)</t>
-  </si>
-  <si>
-    <t>TTM Jul 2025 (gal)</t>
-  </si>
-  <si>
-    <t>Milk Production</t>
-  </si>
-  <si>
-    <t>Annual cwt</t>
-  </si>
-  <si>
-    <t>+4.5%</t>
-  </si>
-  <si>
-    <t>Lbs/Cow/Day</t>
-  </si>
-  <si>
-    <t>+3.2%</t>
-  </si>
-  <si>
-    <t>Milk Quality</t>
-  </si>
-  <si>
-    <t>Butterfat %</t>
-  </si>
-  <si>
-    <t>flat</t>
-  </si>
-  <si>
-    <t>SCC (cells/mL)</t>
-  </si>
-  <si>
-    <t>+25%</t>
-  </si>
-  <si>
-    <t>Plant</t>
-  </si>
-  <si>
-    <t>Utilization Rate</t>
-  </si>
-  <si>
-    <t>Labor Hrs/cwt</t>
-  </si>
-  <si>
-    <t>Crops</t>
-  </si>
-  <si>
-    <t>Corn Silage (t/a)</t>
-  </si>
-  <si>
-    <t>Alfalfa (t/a)</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
-    <t>Operating Margin</t>
-  </si>
-  <si>
-    <t>Total Revenue (Ordinary Income)</t>
-  </si>
-  <si>
-    <t>Total Costs (COGS + OPEx)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -156,22 +52,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -459,210 +414,284 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="7" width="20" customWidth="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TTM Jul 2026</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TTM Jul 2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TTM Jul 2026 (gal)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TTM Jul 2025 (gal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Milk Production</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Annual cwt</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>361247</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>345778</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
       </c>
       <c r="F2">
         <f>C2*11.63</f>
-        <v>4201302.6100000003</v>
+        <v/>
       </c>
       <c r="G2">
         <f>D2*11.63</f>
-        <v>4021398.14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Milk Production</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lbs/Cow/Day</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>96</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>93</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D4">
-        <v>3.9E-2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Milk Quality</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Butterfat %</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Milk Quality</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SCC (cells/mL)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>250000</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>200000</v>
       </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Utilization Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Labor Hrs/cwt</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>0.191</v>
       </c>
       <c r="F7">
         <f>C7/11.63</f>
-        <v>1.642304385210662E-2</v>
+        <v/>
       </c>
       <c r="G7">
         <f>D7/11.63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Crops</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Corn Silage (t/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Crops</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alfalfa (t/a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Total Revenue (Ordinary Income)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>25483840</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>26079541</v>
       </c>
-      <c r="E10">
-        <v>87792</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-2.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Total Costs (COGS + OPEx)</t>
+        </is>
       </c>
       <c r="C11">
-        <f>4341828+20387243</f>
-        <v>24729071</v>
+        <f>4341828+20284250</f>
+        <v/>
       </c>
       <c r="D11">
         <f>7826513+17830008</f>
-        <v>25656521</v>
-      </c>
-      <c r="E11">
-        <v>153407</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12">
-        <v>2.4</v>
-      </c>
-      <c r="D12">
-        <v>2.7</v>
-      </c>
-      <c r="E12">
-        <v>-0.3</v>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operating Margin</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/Key Metrics at a Glance.xlsx
+++ b/data/Key Metrics at a Glance.xlsx
@@ -684,14 +684,17 @@
           <t>Operating Margin</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.8</v>
+      <c r="C12">
+        <f>(C10-C11)/C10*100</f>
+        <v/>
+      </c>
+      <c r="D12">
+        <f>(D10-D11)/D10*100</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>C12-D12</f>
+        <v/>
       </c>
     </row>
   </sheetData>
